--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.04319811408235139</v>
       </c>
       <c r="C2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>34530751</v>
+        <v>3854365</v>
       </c>
       <c r="L2" t="n">
-        <v>19887502</v>
+        <v>1958553</v>
       </c>
       <c r="M2" t="n">
-        <v>5034427</v>
+        <v>442893</v>
       </c>
       <c r="N2" t="n">
-        <v>277630</v>
+        <v>18261</v>
       </c>
       <c r="O2" t="n">
-        <v>3037279</v>
+        <v>282195</v>
       </c>
       <c r="P2" t="n">
-        <v>1238902</v>
+        <v>122802</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999937117099762</v>
+        <v>0.9998652935028076</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8800205588340759</v>
+        <v>0.7857620716094971</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7612059116363525</v>
+        <v>0.5993911027908325</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6868485808372498</v>
+        <v>0.484530121088028</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5097795128822327</v>
+        <v>0.2699015736579895</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7448714971542358</v>
+        <v>0.5538371801376343</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8039232492446899</v>
+        <v>0.6372339725494385</v>
       </c>
       <c r="X2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>33605581</v>
+        <v>3785410</v>
       </c>
       <c r="AG2" t="n">
-        <v>18356699</v>
+        <v>1840830</v>
       </c>
       <c r="AH2" t="n">
-        <v>4567221</v>
+        <v>412538</v>
       </c>
       <c r="AI2" t="n">
-        <v>256703</v>
+        <v>17472</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2789418</v>
+        <v>262478</v>
       </c>
       <c r="AK2" t="n">
-        <v>1165812</v>
+        <v>115591</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.85073322057724</v>
+        <v>0.7666283845901489</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7161439061164856</v>
+        <v>0.5745255947113037</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6164535880088806</v>
+        <v>0.4454534351825714</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3630753755569458</v>
+        <v>0.197696253657341</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6862995624542236</v>
+        <v>0.5166340470314026</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7540320754051208</v>
+        <v>0.5981020927429199</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01237542759378918</v>
       </c>
       <c r="C3" t="n">
-        <v>824</v>
+        <v>260</v>
       </c>
       <c r="D3" t="n">
-        <v>34530751</v>
+        <v>3854365</v>
       </c>
       <c r="E3" t="n">
-        <v>4420444</v>
+        <v>937114</v>
       </c>
       <c r="F3" t="n">
-        <v>192727</v>
+        <v>54800</v>
       </c>
       <c r="G3" t="n">
-        <v>28996</v>
+        <v>6232</v>
       </c>
       <c r="H3" t="n">
-        <v>11774</v>
+        <v>4743</v>
       </c>
       <c r="I3" t="n">
-        <v>1462</v>
+        <v>625</v>
       </c>
       <c r="J3" t="n">
-        <v>78857898</v>
+        <v>9856791</v>
       </c>
       <c r="K3" t="n">
-        <v>84668400</v>
+        <v>10161369</v>
       </c>
       <c r="L3" t="n">
-        <v>96432673</v>
+        <v>11491357</v>
       </c>
       <c r="M3" t="n">
-        <v>118817949</v>
+        <v>14663073</v>
       </c>
       <c r="N3" t="n">
-        <v>127586212</v>
+        <v>15931884</v>
       </c>
       <c r="O3" t="n">
-        <v>123447625</v>
+        <v>15332466</v>
       </c>
       <c r="P3" t="n">
-        <v>126713910</v>
+        <v>15806901</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8811792135238647</v>
+        <v>0.793383002281189</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7681028246879578</v>
+        <v>0.5989412665367126</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6757683753967285</v>
+        <v>0.4730989336967468</v>
       </c>
       <c r="U3" t="n">
-        <v>0.391022652387619</v>
+        <v>0.2049057930707932</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7452958822250366</v>
+        <v>0.5526711344718933</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8007784485816956</v>
+        <v>0.6343406438827515</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33605581</v>
+        <v>3785410</v>
       </c>
       <c r="Z3" t="n">
-        <v>5154314</v>
+        <v>974604</v>
       </c>
       <c r="AA3" t="n">
-        <v>296426</v>
+        <v>72569</v>
       </c>
       <c r="AB3" t="n">
-        <v>110696</v>
+        <v>18171</v>
       </c>
       <c r="AC3" t="n">
-        <v>17504</v>
+        <v>6383</v>
       </c>
       <c r="AD3" t="n">
-        <v>2457</v>
+        <v>1002</v>
       </c>
       <c r="AE3" t="n">
-        <v>78861024</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>83479899</v>
+        <v>10059933</v>
       </c>
       <c r="AG3" t="n">
-        <v>95395485</v>
+        <v>11437118</v>
       </c>
       <c r="AH3" t="n">
-        <v>118271627</v>
+        <v>14620677</v>
       </c>
       <c r="AI3" t="n">
-        <v>127402869</v>
+        <v>15910375</v>
       </c>
       <c r="AJ3" t="n">
-        <v>123212920</v>
+        <v>15314222</v>
       </c>
       <c r="AK3" t="n">
-        <v>126635786</v>
+        <v>15799138</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8575701117515564</v>
+        <v>0.7791892886161804</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7089795470237732</v>
+        <v>0.5629406571388245</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6130555868148804</v>
+        <v>0.4406736791133881</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3615484237670898</v>
+        <v>0.1960524618625641</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6844750642776489</v>
+        <v>0.5140559673309326</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7535359263420105</v>
+        <v>0.5970917940139771</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.09026265231825138</v>
       </c>
       <c r="C4" t="n">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>4427740</v>
+        <v>975561</v>
       </c>
       <c r="E4" t="n">
-        <v>19887502</v>
+        <v>1958553</v>
       </c>
       <c r="F4" t="n">
-        <v>1351254</v>
+        <v>270665</v>
       </c>
       <c r="G4" t="n">
-        <v>50651</v>
+        <v>11744</v>
       </c>
       <c r="H4" t="n">
-        <v>155326</v>
+        <v>46635</v>
       </c>
       <c r="I4" t="n">
-        <v>18916</v>
+        <v>6765</v>
       </c>
       <c r="J4" t="n">
-        <v>3126</v>
+        <v>837</v>
       </c>
       <c r="K4" t="n">
-        <v>4707822</v>
+        <v>1050892</v>
       </c>
       <c r="L4" t="n">
-        <v>6238809</v>
+        <v>1309018</v>
       </c>
       <c r="M4" t="n">
-        <v>2295321</v>
+        <v>471174</v>
       </c>
       <c r="N4" t="n">
-        <v>266978</v>
+        <v>49397</v>
       </c>
       <c r="O4" t="n">
-        <v>1040309</v>
+        <v>227332</v>
       </c>
       <c r="P4" t="n">
-        <v>302168</v>
+        <v>69909</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999685883522034</v>
+        <v>0.9999326467514038</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8805995583534241</v>
+        <v>0.7895541787147522</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7646388411521912</v>
+        <v>0.5991660952568054</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6812633872032166</v>
+        <v>0.4787462949752808</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4425729811191559</v>
+        <v>0.2329550832509995</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7450836300849915</v>
+        <v>0.5532535910606384</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8023477792739868</v>
+        <v>0.6357840299606323</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>5517596</v>
+        <v>1058017</v>
       </c>
       <c r="Z4" t="n">
-        <v>18356699</v>
+        <v>1840830</v>
       </c>
       <c r="AA4" t="n">
-        <v>1669513</v>
+        <v>287515</v>
       </c>
       <c r="AB4" t="n">
-        <v>110467</v>
+        <v>19661</v>
       </c>
       <c r="AC4" t="n">
-        <v>209499</v>
+        <v>55234</v>
       </c>
       <c r="AD4" t="n">
-        <v>27944</v>
+        <v>8768</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>5896323</v>
+        <v>1152328</v>
       </c>
       <c r="AG4" t="n">
-        <v>7275997</v>
+        <v>1363257</v>
       </c>
       <c r="AH4" t="n">
-        <v>2841643</v>
+        <v>513570</v>
       </c>
       <c r="AI4" t="n">
-        <v>450321</v>
+        <v>70906</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1275014</v>
+        <v>245576</v>
       </c>
       <c r="AK4" t="n">
-        <v>380292</v>
+        <v>77672</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8541379570960999</v>
+        <v>0.7728578448295593</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7125437259674072</v>
+        <v>0.5686741471290588</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6147499680519104</v>
+        <v>0.4430506527423859</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3623103201389313</v>
+        <v>0.1968709379434586</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6853861212730408</v>
+        <v>0.5153418183326721</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7537839412689209</v>
+        <v>0.5975965261459351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>584</v>
+        <v>164</v>
       </c>
       <c r="D5" t="n">
-        <v>188694</v>
+        <v>54904</v>
       </c>
       <c r="E5" t="n">
-        <v>1522088</v>
+        <v>293158</v>
       </c>
       <c r="F5" t="n">
-        <v>5034427</v>
+        <v>442893</v>
       </c>
       <c r="G5" t="n">
-        <v>102361</v>
+        <v>17259</v>
       </c>
       <c r="H5" t="n">
-        <v>542198</v>
+        <v>110651</v>
       </c>
       <c r="I5" t="n">
-        <v>59578</v>
+        <v>17124</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4656227</v>
+        <v>1003774</v>
       </c>
       <c r="L5" t="n">
-        <v>6004216</v>
+        <v>1311472</v>
       </c>
       <c r="M5" t="n">
-        <v>2415503</v>
+        <v>493260</v>
       </c>
       <c r="N5" t="n">
-        <v>432380</v>
+        <v>70858</v>
       </c>
       <c r="O5" t="n">
-        <v>1037987</v>
+        <v>228407</v>
       </c>
       <c r="P5" t="n">
-        <v>308220</v>
+        <v>70788</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999756813049316</v>
+        <v>0.9999479055404663</v>
       </c>
       <c r="R5" t="n">
-        <v>0.92716383934021</v>
+        <v>0.87214595079422</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9047703742980957</v>
+        <v>0.8369368314743042</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9633579254150391</v>
+        <v>0.9399869441986084</v>
       </c>
       <c r="U5" t="n">
-        <v>0.994560182094574</v>
+        <v>0.9925169944763184</v>
       </c>
       <c r="V5" t="n">
-        <v>0.983834445476532</v>
+        <v>0.9716410636901855</v>
       </c>
       <c r="W5" t="n">
-        <v>0.995252251625061</v>
+        <v>0.9912449717521667</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>260643</v>
+        <v>69548</v>
       </c>
       <c r="Z5" t="n">
-        <v>1757599</v>
+        <v>299719</v>
       </c>
       <c r="AA5" t="n">
-        <v>4567221</v>
+        <v>412538</v>
       </c>
       <c r="AB5" t="n">
-        <v>128521</v>
+        <v>18569</v>
       </c>
       <c r="AC5" t="n">
-        <v>656535</v>
+        <v>116001</v>
       </c>
       <c r="AD5" t="n">
-        <v>79411</v>
+        <v>19778</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>5581397</v>
+        <v>1072729</v>
       </c>
       <c r="AG5" t="n">
-        <v>7535019</v>
+        <v>1429195</v>
       </c>
       <c r="AH5" t="n">
-        <v>2882709</v>
+        <v>523615</v>
       </c>
       <c r="AI5" t="n">
-        <v>453307</v>
+        <v>71647</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1285848</v>
+        <v>248124</v>
       </c>
       <c r="AK5" t="n">
-        <v>381310</v>
+        <v>77999</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9107231497764587</v>
+        <v>0.8615431189537048</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8847958445549011</v>
+        <v>0.8262363076210022</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9554744362831116</v>
+        <v>0.9354599118232727</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9929713606834412</v>
+        <v>0.991129457950592</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9800809025764465</v>
+        <v>0.9692789316177368</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9940760731697083</v>
+        <v>0.9903131723403931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>967</v>
+        <v>211</v>
       </c>
       <c r="D6" t="n">
-        <v>81422</v>
+        <v>15254</v>
       </c>
       <c r="E6" t="n">
-        <v>115875</v>
+        <v>21418</v>
       </c>
       <c r="F6" t="n">
-        <v>144703</v>
+        <v>18619</v>
       </c>
       <c r="G6" t="n">
-        <v>277630</v>
+        <v>18261</v>
       </c>
       <c r="H6" t="n">
-        <v>77655</v>
+        <v>12700</v>
       </c>
       <c r="I6" t="n">
-        <v>11758</v>
+        <v>2656</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>99647</v>
+        <v>16519</v>
       </c>
       <c r="Z6" t="n">
-        <v>116686</v>
+        <v>21042</v>
       </c>
       <c r="AA6" t="n">
-        <v>134966</v>
+        <v>18533</v>
       </c>
       <c r="AB6" t="n">
-        <v>256703</v>
+        <v>17472</v>
       </c>
       <c r="AC6" t="n">
-        <v>87764</v>
+        <v>12698</v>
       </c>
       <c r="AD6" t="n">
-        <v>14244</v>
+        <v>2855</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>247</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
-        <v>9567</v>
+        <v>5062</v>
       </c>
       <c r="E7" t="n">
-        <v>167258</v>
+        <v>52149</v>
       </c>
       <c r="F7" t="n">
-        <v>573386</v>
+        <v>116406</v>
       </c>
       <c r="G7" t="n">
-        <v>77075</v>
+        <v>11982</v>
       </c>
       <c r="H7" t="n">
-        <v>3037279</v>
+        <v>282195</v>
       </c>
       <c r="I7" t="n">
-        <v>210454</v>
+        <v>42739</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>17739</v>
+        <v>7990</v>
       </c>
       <c r="Z7" t="n">
-        <v>227580</v>
+        <v>61043</v>
       </c>
       <c r="AA7" t="n">
-        <v>694428</v>
+        <v>121849</v>
       </c>
       <c r="AB7" t="n">
-        <v>89865</v>
+        <v>11973</v>
       </c>
       <c r="AC7" t="n">
-        <v>2789418</v>
+        <v>262478</v>
       </c>
       <c r="AD7" t="n">
-        <v>256236</v>
+        <v>45269</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>111</v>
       </c>
       <c r="E8" t="n">
-        <v>13144</v>
+        <v>5179</v>
       </c>
       <c r="F8" t="n">
-        <v>33251</v>
+        <v>10684</v>
       </c>
       <c r="G8" t="n">
-        <v>7895</v>
+        <v>2180</v>
       </c>
       <c r="H8" t="n">
-        <v>253356</v>
+        <v>52603</v>
       </c>
       <c r="I8" t="n">
-        <v>1238902</v>
+        <v>122802</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>698</v>
+        <v>254</v>
       </c>
       <c r="Z8" t="n">
-        <v>19818</v>
+        <v>6849</v>
       </c>
       <c r="AA8" t="n">
-        <v>46310</v>
+        <v>13104</v>
       </c>
       <c r="AB8" t="n">
-        <v>10772</v>
+        <v>2532</v>
       </c>
       <c r="AC8" t="n">
-        <v>303712</v>
+        <v>55260</v>
       </c>
       <c r="AD8" t="n">
-        <v>1165812</v>
+        <v>115591</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
